--- a/outputs/50324.xlsx
+++ b/outputs/50324.xlsx
@@ -141,10 +141,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0&quot; €&quot;;\-#,##0&quot; €&quot;"/>
-    <numFmt numFmtId="166" formatCode="0.#########"/>
+    <numFmt numFmtId="166" formatCode="0"/>
+    <numFmt numFmtId="167" formatCode="0.##########"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -239,28 +240,32 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1481,25 +1486,25 @@
       <c r="D5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="E5" s="6" t="n">
         <v>0.733333333333333</v>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="F5" s="6" t="n">
         <v>0.833333333333333</v>
       </c>
-      <c r="G5" s="5" t="n">
+      <c r="G5" s="6" t="n">
         <v>0.7</v>
       </c>
-      <c r="H5" s="5" t="n">
+      <c r="H5" s="6" t="n">
         <v>0.866666666666667</v>
       </c>
-      <c r="I5" s="5" t="n">
+      <c r="I5" s="6" t="n">
         <v>0.566666666666667</v>
       </c>
-      <c r="J5" s="5" t="n">
+      <c r="J5" s="6" t="n">
         <v>0.9</v>
       </c>
-      <c r="K5" s="5" t="n">
+      <c r="K5" s="6" t="n">
         <v>0.433333333333333</v>
       </c>
     </row>
@@ -1507,28 +1512,28 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="5" t="n">
+      <c r="D6" s="6" t="n">
         <v>0.733333333333333</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F6" s="6" t="n">
         <v>0.7</v>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="G6" s="6" t="n">
         <v>0.666666666666667</v>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="H6" s="6" t="n">
         <v>0.7</v>
       </c>
-      <c r="I6" s="5" t="n">
+      <c r="I6" s="6" t="n">
         <v>0.533333333333333</v>
       </c>
-      <c r="J6" s="5" t="n">
+      <c r="J6" s="6" t="n">
         <v>0.733333333333333</v>
       </c>
-      <c r="K6" s="5" t="n">
+      <c r="K6" s="6" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -1536,28 +1541,28 @@
       <c r="C7" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D7" s="5" t="n">
+      <c r="D7" s="6" t="n">
         <v>0.833333333333333</v>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" s="6" t="n">
         <v>0.7</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="G7" s="6" t="n">
         <v>0.7</v>
       </c>
-      <c r="H7" s="5" t="n">
+      <c r="H7" s="6" t="n">
         <v>0.833333333333333</v>
       </c>
-      <c r="I7" s="5" t="n">
+      <c r="I7" s="6" t="n">
         <v>0.566666666666667</v>
       </c>
-      <c r="J7" s="5" t="n">
+      <c r="J7" s="6" t="n">
         <v>0.833333333333333</v>
       </c>
-      <c r="K7" s="5" t="n">
+      <c r="K7" s="6" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -1565,28 +1570,28 @@
       <c r="C8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="5" t="n">
+      <c r="D8" s="6" t="n">
         <v>0.7</v>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="E8" s="6" t="n">
         <v>0.666666666666667</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F8" s="6" t="n">
         <v>0.7</v>
       </c>
       <c r="G8" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H8" s="5" t="n">
+      <c r="H8" s="6" t="n">
         <v>0.7</v>
       </c>
-      <c r="I8" s="5" t="n">
+      <c r="I8" s="6" t="n">
         <v>0.533333333333333</v>
       </c>
-      <c r="J8" s="5" t="n">
+      <c r="J8" s="6" t="n">
         <v>0.7</v>
       </c>
-      <c r="K8" s="5" t="n">
+      <c r="K8" s="6" t="n">
         <v>0.366666666666667</v>
       </c>
     </row>
@@ -1594,28 +1599,28 @@
       <c r="C9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="5" t="n">
+      <c r="D9" s="6" t="n">
         <v>0.866666666666667</v>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="E9" s="6" t="n">
         <v>0.7</v>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="F9" s="6" t="n">
         <v>0.833333333333333</v>
       </c>
-      <c r="G9" s="5" t="n">
+      <c r="G9" s="6" t="n">
         <v>0.7</v>
       </c>
       <c r="H9" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I9" s="5" t="n">
+      <c r="I9" s="6" t="n">
         <v>0.566666666666667</v>
       </c>
-      <c r="J9" s="5" t="n">
+      <c r="J9" s="6" t="n">
         <v>0.866666666666667</v>
       </c>
-      <c r="K9" s="5" t="n">
+      <c r="K9" s="6" t="n">
         <v>0.433333333333333</v>
       </c>
     </row>
@@ -1623,28 +1628,28 @@
       <c r="C10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="5" t="n">
+      <c r="D10" s="6" t="n">
         <v>0.566666666666667</v>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="E10" s="6" t="n">
         <v>0.533333333333333</v>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="F10" s="6" t="n">
         <v>0.566666666666667</v>
       </c>
-      <c r="G10" s="5" t="n">
+      <c r="G10" s="6" t="n">
         <v>0.533333333333333</v>
       </c>
-      <c r="H10" s="5" t="n">
+      <c r="H10" s="6" t="n">
         <v>0.566666666666667</v>
       </c>
       <c r="I10" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="J10" s="5" t="n">
+      <c r="J10" s="6" t="n">
         <v>0.566666666666667</v>
       </c>
-      <c r="K10" s="5" t="n">
+      <c r="K10" s="6" t="n">
         <v>0.333333333333333</v>
       </c>
     </row>
@@ -1652,28 +1657,28 @@
       <c r="C11" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D11" s="5" t="n">
+      <c r="D11" s="6" t="n">
         <v>0.9</v>
       </c>
-      <c r="E11" s="5" t="n">
+      <c r="E11" s="6" t="n">
         <v>0.733333333333333</v>
       </c>
-      <c r="F11" s="5" t="n">
+      <c r="F11" s="6" t="n">
         <v>0.833333333333333</v>
       </c>
-      <c r="G11" s="5" t="n">
+      <c r="G11" s="6" t="n">
         <v>0.7</v>
       </c>
-      <c r="H11" s="5" t="n">
+      <c r="H11" s="6" t="n">
         <v>0.866666666666667</v>
       </c>
-      <c r="I11" s="5" t="n">
+      <c r="I11" s="6" t="n">
         <v>0.566666666666667</v>
       </c>
       <c r="J11" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="K11" s="5" t="n">
+      <c r="K11" s="6" t="n">
         <v>0.433333333333333</v>
       </c>
     </row>
@@ -1681,25 +1686,25 @@
       <c r="C12" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="5" t="n">
+      <c r="D12" s="6" t="n">
         <v>0.433333333333333</v>
       </c>
-      <c r="E12" s="5" t="n">
+      <c r="E12" s="6" t="n">
         <v>0.4</v>
       </c>
-      <c r="F12" s="5" t="n">
+      <c r="F12" s="6" t="n">
         <v>0.4</v>
       </c>
-      <c r="G12" s="5" t="n">
+      <c r="G12" s="6" t="n">
         <v>0.366666666666667</v>
       </c>
-      <c r="H12" s="5" t="n">
+      <c r="H12" s="6" t="n">
         <v>0.433333333333333</v>
       </c>
-      <c r="I12" s="5" t="n">
+      <c r="I12" s="6" t="n">
         <v>0.333333333333333</v>
       </c>
-      <c r="J12" s="5" t="n">
+      <c r="J12" s="6" t="n">
         <v>0.433333333333333</v>
       </c>
       <c r="K12" s="5" t="n">

--- a/outputs/50324.xlsx
+++ b/outputs/50324.xlsx
@@ -141,11 +141,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0&quot; €&quot;;\-#,##0&quot; €&quot;"/>
-    <numFmt numFmtId="166" formatCode="0"/>
-    <numFmt numFmtId="167" formatCode="0.##########"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -240,7 +238,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -261,11 +259,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -528,7 +522,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="12" style="1" width="8.67"/>
   </cols>
   <sheetData>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C3" s="2"/>
       <c r="D3" s="3" t="s">
         <v>0</v>
@@ -555,7 +549,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C4" s="2" t="s">
         <v>8</v>
       </c>
@@ -584,7 +578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C5" s="2" t="s">
         <v>9</v>
       </c>
@@ -613,7 +607,7 @@
         <v>538954.04075</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C6" s="2" t="s">
         <v>10</v>
       </c>
@@ -642,7 +636,7 @@
         <v>565349.51562</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C7" s="2" t="s">
         <v>11</v>
       </c>
@@ -671,7 +665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C8" s="2" t="s">
         <v>12</v>
       </c>
@@ -700,7 +694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C9" s="2" t="s">
         <v>13</v>
       </c>
@@ -729,7 +723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C10" s="2" t="s">
         <v>14</v>
       </c>
@@ -758,7 +752,7 @@
         <v>451437.958026</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C11" s="2" t="s">
         <v>15</v>
       </c>
@@ -787,7 +781,7 @@
         <v>37805.32616</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C12" s="2" t="s">
         <v>16</v>
       </c>
@@ -816,7 +810,7 @@
         <v>786419.468034</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C13" s="2" t="s">
         <v>17</v>
       </c>
@@ -845,7 +839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C14" s="2" t="s">
         <v>18</v>
       </c>
@@ -874,7 +868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C15" s="2" t="s">
         <v>19</v>
       </c>
@@ -903,7 +897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C16" s="2" t="s">
         <v>20</v>
       </c>
@@ -932,7 +926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C17" s="2" t="s">
         <v>21</v>
       </c>
@@ -961,7 +955,7 @@
         <v>16416.9093</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C18" s="2" t="s">
         <v>22</v>
       </c>
@@ -990,7 +984,7 @@
         <v>452010.607778</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C19" s="2" t="s">
         <v>23</v>
       </c>
@@ -1019,7 +1013,7 @@
         <v>267262.24032</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C20" s="2" t="s">
         <v>24</v>
       </c>
@@ -1048,7 +1042,7 @@
         <v>27053.94496</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C21" s="2" t="s">
         <v>25</v>
       </c>
@@ -1077,7 +1071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C22" s="2" t="s">
         <v>26</v>
       </c>
@@ -1106,7 +1100,7 @@
         <v>95807.57952</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C23" s="2" t="s">
         <v>27</v>
       </c>
@@ -1135,7 +1129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C24" s="2" t="s">
         <v>28</v>
       </c>
@@ -1164,7 +1158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C25" s="2" t="s">
         <v>29</v>
       </c>
@@ -1193,7 +1187,7 @@
         <v>14078.02068</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C26" s="2" t="s">
         <v>30</v>
       </c>
@@ -1222,7 +1216,7 @@
         <v>11897.001192</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C27" s="2" t="s">
         <v>31</v>
       </c>
@@ -1251,7 +1245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C28" s="2" t="s">
         <v>32</v>
       </c>
@@ -1280,7 +1274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C29" s="2" t="s">
         <v>33</v>
       </c>
@@ -1309,7 +1303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C30" s="2" t="s">
         <v>34</v>
       </c>
@@ -1338,7 +1332,7 @@
         <v>22722.572768</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C31" s="2" t="s">
         <v>35</v>
       </c>
@@ -1367,7 +1361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C32" s="2" t="s">
         <v>36</v>
       </c>
@@ -1396,7 +1390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C33" s="2" t="s">
         <v>37</v>
       </c>
@@ -1452,7 +1446,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="6.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C4" s="2"/>
       <c r="D4" s="3" t="s">
         <v>0</v>
@@ -1486,25 +1480,32 @@
       <c r="D5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="E5" s="5" t="n">
+        <f aca="false">SUMPRODUCT((Datensatz!$D4:$D33&gt;0)*(Datensatz!$E4:$E33&gt;0))/30</f>
         <v>0.733333333333333</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F5" s="5" t="n">
+        <f aca="false">SUMPRODUCT((Datensatz!$D4:$D33&gt;0)*(Datensatz!$F4:$F33&gt;0))/30</f>
         <v>0.833333333333333</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="G5" s="5" t="n">
+        <f aca="false">SUMPRODUCT((Datensatz!$D4:$D33&gt;0)*(Datensatz!$G4:$G33&gt;0))/30</f>
         <v>0.7</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="H5" s="5" t="n">
+        <f aca="false">SUMPRODUCT((Datensatz!$D4:$D33&gt;0)*(Datensatz!$H4:$H33&gt;0))/30</f>
         <v>0.866666666666667</v>
       </c>
-      <c r="I5" s="6" t="n">
+      <c r="I5" s="5" t="n">
+        <f aca="false">SUMPRODUCT((Datensatz!$D4:$D33&gt;0)*(Datensatz!$I4:$I33&gt;0))/30</f>
         <v>0.566666666666667</v>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="J5" s="5" t="n">
+        <f aca="false">SUMPRODUCT((Datensatz!$D4:$D33&gt;0)*(Datensatz!$J4:$J33&gt;0))/30</f>
         <v>0.9</v>
       </c>
-      <c r="K5" s="6" t="n">
+      <c r="K5" s="5" t="n">
+        <f aca="false">SUMPRODUCT((Datensatz!$D4:$D33&gt;0)*(Datensatz!$K4:$K33&gt;0))/30</f>
         <v>0.433333333333333</v>
       </c>
     </row>
@@ -1512,28 +1513,35 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="5" t="n">
+        <f aca="false">SUMPRODUCT((Datensatz!$E4:$E33&gt;0)*(Datensatz!$D4:$D33&gt;0))/30</f>
         <v>0.733333333333333</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="F6" s="5" t="n">
+        <f aca="false">SUMPRODUCT((Datensatz!$E4:$E33&gt;0)*(Datensatz!$F4:$F33&gt;0))/30</f>
         <v>0.7</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="G6" s="5" t="n">
+        <f aca="false">SUMPRODUCT((Datensatz!$E4:$E33&gt;0)*(Datensatz!$G4:$G33&gt;0))/30</f>
         <v>0.666666666666667</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="H6" s="5" t="n">
+        <f aca="false">SUMPRODUCT((Datensatz!$E4:$E33&gt;0)*(Datensatz!$H4:$H33&gt;0))/30</f>
         <v>0.7</v>
       </c>
-      <c r="I6" s="6" t="n">
+      <c r="I6" s="5" t="n">
+        <f aca="false">SUMPRODUCT((Datensatz!$E4:$E33&gt;0)*(Datensatz!$I4:$I33&gt;0))/30</f>
         <v>0.533333333333333</v>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="J6" s="5" t="n">
+        <f aca="false">SUMPRODUCT((Datensatz!$E4:$E33&gt;0)*(Datensatz!$J4:$J33&gt;0))/30</f>
         <v>0.733333333333333</v>
       </c>
-      <c r="K6" s="6" t="n">
+      <c r="K6" s="5" t="n">
+        <f aca="false">SUMPRODUCT((Datensatz!$E4:$E33&gt;0)*(Datensatz!$K4:$K33&gt;0))/30</f>
         <v>0.4</v>
       </c>
     </row>
@@ -1541,28 +1549,35 @@
       <c r="C7" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="5" t="n">
+        <f aca="false">SUMPRODUCT((Datensatz!$F4:$F33&gt;0)*(Datensatz!$D4:$D33&gt;0))/30</f>
         <v>0.833333333333333</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="E7" s="5" t="n">
+        <f aca="false">SUMPRODUCT((Datensatz!$F4:$F33&gt;0)*(Datensatz!$E4:$E33&gt;0))/30</f>
         <v>0.7</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="G7" s="5" t="n">
+        <f aca="false">SUMPRODUCT((Datensatz!$F4:$F33&gt;0)*(Datensatz!$G4:$G33&gt;0))/30</f>
         <v>0.7</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="H7" s="5" t="n">
+        <f aca="false">SUMPRODUCT((Datensatz!$F4:$F33&gt;0)*(Datensatz!$H4:$H33&gt;0))/30</f>
         <v>0.833333333333333</v>
       </c>
-      <c r="I7" s="6" t="n">
+      <c r="I7" s="5" t="n">
+        <f aca="false">SUMPRODUCT((Datensatz!$F4:$F33&gt;0)*(Datensatz!$I4:$I33&gt;0))/30</f>
         <v>0.566666666666667</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="J7" s="5" t="n">
+        <f aca="false">SUMPRODUCT((Datensatz!$F4:$F33&gt;0)*(Datensatz!$J4:$J33&gt;0))/30</f>
         <v>0.833333333333333</v>
       </c>
-      <c r="K7" s="6" t="n">
+      <c r="K7" s="5" t="n">
+        <f aca="false">SUMPRODUCT((Datensatz!$F4:$F33&gt;0)*(Datensatz!$K4:$K33&gt;0))/30</f>
         <v>0.4</v>
       </c>
     </row>
@@ -1570,28 +1585,35 @@
       <c r="C8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="5" t="n">
+        <f aca="false">SUMPRODUCT((Datensatz!$G4:$G33&gt;0)*(Datensatz!$D4:$D33&gt;0))/30</f>
         <v>0.7</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="E8" s="5" t="n">
+        <f aca="false">SUMPRODUCT((Datensatz!$G4:$G33&gt;0)*(Datensatz!$E4:$E33&gt;0))/30</f>
         <v>0.666666666666667</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="F8" s="5" t="n">
+        <f aca="false">SUMPRODUCT((Datensatz!$G4:$G33&gt;0)*(Datensatz!$F4:$F33&gt;0))/30</f>
         <v>0.7</v>
       </c>
       <c r="G8" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="H8" s="5" t="n">
+        <f aca="false">SUMPRODUCT((Datensatz!$G4:$G33&gt;0)*(Datensatz!$H4:$H33&gt;0))/30</f>
         <v>0.7</v>
       </c>
-      <c r="I8" s="6" t="n">
+      <c r="I8" s="5" t="n">
+        <f aca="false">SUMPRODUCT((Datensatz!$G4:$G33&gt;0)*(Datensatz!$I4:$I33&gt;0))/30</f>
         <v>0.533333333333333</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="J8" s="5" t="n">
+        <f aca="false">SUMPRODUCT((Datensatz!$G4:$G33&gt;0)*(Datensatz!$J4:$J33&gt;0))/30</f>
         <v>0.7</v>
       </c>
-      <c r="K8" s="6" t="n">
+      <c r="K8" s="5" t="n">
+        <f aca="false">SUMPRODUCT((Datensatz!$G4:$G33&gt;0)*(Datensatz!$K4:$K33&gt;0))/30</f>
         <v>0.366666666666667</v>
       </c>
     </row>
@@ -1599,28 +1621,35 @@
       <c r="C9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="5" t="n">
+        <f aca="false">SUMPRODUCT((Datensatz!$H4:$H33&gt;0)*(Datensatz!$D4:$D33&gt;0))/30</f>
         <v>0.866666666666667</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="E9" s="5" t="n">
+        <f aca="false">SUMPRODUCT((Datensatz!$H4:$H33&gt;0)*(Datensatz!$E4:$E33&gt;0))/30</f>
         <v>0.7</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="F9" s="5" t="n">
+        <f aca="false">SUMPRODUCT((Datensatz!$H4:$H33&gt;0)*(Datensatz!$F4:$F33&gt;0))/30</f>
         <v>0.833333333333333</v>
       </c>
-      <c r="G9" s="6" t="n">
+      <c r="G9" s="5" t="n">
+        <f aca="false">SUMPRODUCT((Datensatz!$H4:$H33&gt;0)*(Datensatz!$G4:$G33&gt;0))/30</f>
         <v>0.7</v>
       </c>
       <c r="H9" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I9" s="6" t="n">
+      <c r="I9" s="5" t="n">
+        <f aca="false">SUMPRODUCT((Datensatz!$H4:$H33&gt;0)*(Datensatz!$I4:$I33&gt;0))/30</f>
         <v>0.566666666666667</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="J9" s="5" t="n">
+        <f aca="false">SUMPRODUCT((Datensatz!$H4:$H33&gt;0)*(Datensatz!$J4:$J33&gt;0))/30</f>
         <v>0.866666666666667</v>
       </c>
-      <c r="K9" s="6" t="n">
+      <c r="K9" s="5" t="n">
+        <f aca="false">SUMPRODUCT((Datensatz!$H4:$H33&gt;0)*(Datensatz!$K4:$K33&gt;0))/30</f>
         <v>0.433333333333333</v>
       </c>
     </row>
@@ -1628,28 +1657,35 @@
       <c r="C10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="5" t="n">
+        <f aca="false">SUMPRODUCT((Datensatz!$I4:$I33&gt;0)*(Datensatz!$D4:$D33&gt;0))/30</f>
         <v>0.566666666666667</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="E10" s="5" t="n">
+        <f aca="false">SUMPRODUCT((Datensatz!$I4:$I33&gt;0)*(Datensatz!$E4:$E33&gt;0))/30</f>
         <v>0.533333333333333</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="F10" s="5" t="n">
+        <f aca="false">SUMPRODUCT((Datensatz!$I4:$I33&gt;0)*(Datensatz!$F4:$F33&gt;0))/30</f>
         <v>0.566666666666667</v>
       </c>
-      <c r="G10" s="6" t="n">
+      <c r="G10" s="5" t="n">
+        <f aca="false">SUMPRODUCT((Datensatz!$I4:$I33&gt;0)*(Datensatz!$G4:$G33&gt;0))/30</f>
         <v>0.533333333333333</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="H10" s="5" t="n">
+        <f aca="false">SUMPRODUCT((Datensatz!$I4:$I33&gt;0)*(Datensatz!$H4:$H33&gt;0))/30</f>
         <v>0.566666666666667</v>
       </c>
       <c r="I10" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="J10" s="5" t="n">
+        <f aca="false">SUMPRODUCT((Datensatz!$I4:$I33&gt;0)*(Datensatz!$J4:$J33&gt;0))/30</f>
         <v>0.566666666666667</v>
       </c>
-      <c r="K10" s="6" t="n">
+      <c r="K10" s="5" t="n">
+        <f aca="false">SUMPRODUCT((Datensatz!$I4:$I33&gt;0)*(Datensatz!$K4:$K33&gt;0))/30</f>
         <v>0.333333333333333</v>
       </c>
     </row>
@@ -1657,28 +1693,35 @@
       <c r="C11" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="5" t="n">
+        <f aca="false">SUMPRODUCT((Datensatz!$J4:$J33&gt;0)*(Datensatz!$D4:$D33&gt;0))/30</f>
         <v>0.9</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="E11" s="5" t="n">
+        <f aca="false">SUMPRODUCT((Datensatz!$J4:$J33&gt;0)*(Datensatz!$E4:$E33&gt;0))/30</f>
         <v>0.733333333333333</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="F11" s="5" t="n">
+        <f aca="false">SUMPRODUCT((Datensatz!$J4:$J33&gt;0)*(Datensatz!$F4:$F33&gt;0))/30</f>
         <v>0.833333333333333</v>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="G11" s="5" t="n">
+        <f aca="false">SUMPRODUCT((Datensatz!$J4:$J33&gt;0)*(Datensatz!$G4:$G33&gt;0))/30</f>
         <v>0.7</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="H11" s="5" t="n">
+        <f aca="false">SUMPRODUCT((Datensatz!$J4:$J33&gt;0)*(Datensatz!$H4:$H33&gt;0))/30</f>
         <v>0.866666666666667</v>
       </c>
-      <c r="I11" s="6" t="n">
+      <c r="I11" s="5" t="n">
+        <f aca="false">SUMPRODUCT((Datensatz!$J4:$J33&gt;0)*(Datensatz!$I4:$I33&gt;0))/30</f>
         <v>0.566666666666667</v>
       </c>
       <c r="J11" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="K11" s="6" t="n">
+      <c r="K11" s="5" t="n">
+        <f aca="false">SUMPRODUCT((Datensatz!$J4:$J33&gt;0)*(Datensatz!$K4:$K33&gt;0))/30</f>
         <v>0.433333333333333</v>
       </c>
     </row>
@@ -1686,25 +1729,32 @@
       <c r="C12" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D12" s="5" t="n">
+        <f aca="false">SUMPRODUCT((Datensatz!$K4:$K33&gt;0)*(Datensatz!$D4:$D33&gt;0))/30</f>
         <v>0.433333333333333</v>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="E12" s="5" t="n">
+        <f aca="false">SUMPRODUCT((Datensatz!$K4:$K33&gt;0)*(Datensatz!$E4:$E33&gt;0))/30</f>
         <v>0.4</v>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="F12" s="5" t="n">
+        <f aca="false">SUMPRODUCT((Datensatz!$K4:$K33&gt;0)*(Datensatz!$F4:$F33&gt;0))/30</f>
         <v>0.4</v>
       </c>
-      <c r="G12" s="6" t="n">
+      <c r="G12" s="5" t="n">
+        <f aca="false">SUMPRODUCT((Datensatz!$K4:$K33&gt;0)*(Datensatz!$G4:$G33&gt;0))/30</f>
         <v>0.366666666666667</v>
       </c>
-      <c r="H12" s="6" t="n">
+      <c r="H12" s="5" t="n">
+        <f aca="false">SUMPRODUCT((Datensatz!$K4:$K33&gt;0)*(Datensatz!$H4:$H33&gt;0))/30</f>
         <v>0.433333333333333</v>
       </c>
-      <c r="I12" s="6" t="n">
+      <c r="I12" s="5" t="n">
+        <f aca="false">SUMPRODUCT((Datensatz!$K4:$K33&gt;0)*(Datensatz!$I4:$I33&gt;0))/30</f>
         <v>0.333333333333333</v>
       </c>
-      <c r="J12" s="6" t="n">
+      <c r="J12" s="5" t="n">
+        <f aca="false">SUMPRODUCT((Datensatz!$K4:$K33&gt;0)*(Datensatz!$J4:$J33&gt;0))/30</f>
         <v>0.433333333333333</v>
       </c>
       <c r="K12" s="5" t="n">
